--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="159">
   <si>
     <t>#</t>
   </si>
@@ -90,6 +90,9 @@
     <t>Max</t>
   </si>
   <si>
+    <t>Number</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -105,6 +108,18 @@
     <t>每百层大概50个</t>
   </si>
   <si>
+    <t>副本劵*2</t>
+  </si>
+  <si>
+    <t>220021</t>
+  </si>
+  <si>
+    <t>传世劵</t>
+  </si>
+  <si>
+    <t>100层掉一个</t>
+  </si>
+  <si>
     <t>220001</t>
   </si>
   <si>
@@ -114,6 +129,156 @@
     <t>每百层大概5个</t>
   </si>
   <si>
+    <t>Boss劵*2</t>
+  </si>
+  <si>
+    <t>220012</t>
+  </si>
+  <si>
+    <t>彻地钉</t>
+  </si>
+  <si>
+    <t>250层,1/7掉落</t>
+  </si>
+  <si>
+    <t>220014</t>
+  </si>
+  <si>
+    <t>无极道体</t>
+  </si>
+  <si>
+    <t>250层,1/10掉落</t>
+  </si>
+  <si>
+    <t>220015</t>
+  </si>
+  <si>
+    <t>分身术</t>
+  </si>
+  <si>
+    <t>220029</t>
+  </si>
+  <si>
+    <t>战士之魂</t>
+  </si>
+  <si>
+    <t>220030</t>
+  </si>
+  <si>
+    <t>法师之魂</t>
+  </si>
+  <si>
+    <t>220031</t>
+  </si>
+  <si>
+    <t>道士之魂</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>红装精华</t>
+  </si>
+  <si>
+    <t>打完500层，3天一个</t>
+  </si>
+  <si>
+    <t>220013</t>
+  </si>
+  <si>
+    <t>高级书页</t>
+  </si>
+  <si>
+    <t>220038</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
+  </si>
+  <si>
+    <t>220041</t>
+  </si>
+  <si>
+    <t>改造石</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>金色精华</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>暗金精华</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>开孔石</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>时装精华</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>超级书页</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>不朽精华</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>永恒精华</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>混沌精华</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
+    <t>随机宝石</t>
+  </si>
+  <si>
+    <t>220036</t>
+  </si>
+  <si>
+    <t>等级丹*10</t>
+  </si>
+  <si>
+    <t>每百层大概2.5个</t>
+  </si>
+  <si>
+    <t>220037</t>
+  </si>
+  <si>
+    <t>等级丹*15</t>
+  </si>
+  <si>
+    <t>等级丹*20</t>
+  </si>
+  <si>
     <t>220002</t>
   </si>
   <si>
@@ -138,10 +303,10 @@
     <t>2000</t>
   </si>
   <si>
-    <t>沙城图鉴</t>
-  </si>
-  <si>
-    <t>2006</t>
+    <t>龙城图鉴</t>
+  </si>
+  <si>
+    <t>2005</t>
   </si>
   <si>
     <t>红色图鉴</t>
@@ -156,19 +321,34 @@
     <t>二期时装</t>
   </si>
   <si>
-    <t>220012</t>
-  </si>
-  <si>
-    <t>彻地钉</t>
-  </si>
-  <si>
-    <t>250层,1/7掉落</t>
-  </si>
-  <si>
-    <t>220013</t>
-  </si>
-  <si>
-    <t>高级书页</t>
+    <t>三期时装</t>
+  </si>
+  <si>
+    <t>暗金时装</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>金图鉴1</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>金图鉴2</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>金图鉴3</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>暗金图鉴</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -217,6 +397,147 @@
   </si>
   <si>
     <t>财富契约</t>
+  </si>
+  <si>
+    <t>传世之源</t>
+  </si>
+  <si>
+    <t>神戒之源</t>
+  </si>
+  <si>
+    <t>传世契约</t>
+  </si>
+  <si>
+    <t>极·卖身契</t>
+  </si>
+  <si>
+    <t>10倍数，低概率掉落</t>
+  </si>
+  <si>
+    <t>极·副本契约</t>
+  </si>
+  <si>
+    <t>极·BOSS契约</t>
+  </si>
+  <si>
+    <t>极.财富契约</t>
+  </si>
+  <si>
+    <t>极.魔法书</t>
+  </si>
+  <si>
+    <t>极.无限之魂</t>
+  </si>
+  <si>
+    <t>极·传世契约</t>
+  </si>
+  <si>
+    <t>极·万界图</t>
+  </si>
+  <si>
+    <t>极·金蛟剪</t>
+  </si>
+  <si>
+    <t>极·炼体证明</t>
+  </si>
+  <si>
+    <t>极·炼气证明</t>
+  </si>
+  <si>
+    <t>极·炼神证明</t>
+  </si>
+  <si>
+    <t>220016</t>
+  </si>
+  <si>
+    <t>六大神戒</t>
+  </si>
+  <si>
+    <t>4001</t>
+  </si>
+  <si>
+    <t>神技</t>
+  </si>
+  <si>
+    <t>4002</t>
+  </si>
+  <si>
+    <t>魂骨</t>
+  </si>
+  <si>
+    <t>220101</t>
+  </si>
+  <si>
+    <t>白色宠物</t>
+  </si>
+  <si>
+    <t>1天一个</t>
+  </si>
+  <si>
+    <t>220102</t>
+  </si>
+  <si>
+    <t>绿色宠物</t>
+  </si>
+  <si>
+    <t>2天一个</t>
+  </si>
+  <si>
+    <t>220103</t>
+  </si>
+  <si>
+    <t>蓝色宠物</t>
+  </si>
+  <si>
+    <t>3天一个</t>
+  </si>
+  <si>
+    <t>220104</t>
+  </si>
+  <si>
+    <t>紫色宠物</t>
+  </si>
+  <si>
+    <t>4天一个</t>
+  </si>
+  <si>
+    <t>220105</t>
+  </si>
+  <si>
+    <t>橙色宠物</t>
+  </si>
+  <si>
+    <t>5天一个</t>
+  </si>
+  <si>
+    <t>220106</t>
+  </si>
+  <si>
+    <t>红色宠物</t>
+  </si>
+  <si>
+    <t>6天一个</t>
+  </si>
+  <si>
+    <t>220107</t>
+  </si>
+  <si>
+    <t>金色宠物</t>
+  </si>
+  <si>
+    <t>7天一个</t>
+  </si>
+  <si>
+    <t>220042</t>
+  </si>
+  <si>
+    <t>暗金魂心</t>
+  </si>
+  <si>
+    <t>220043</t>
+  </si>
+  <si>
+    <t>六大极戒</t>
   </si>
 </sst>
 </file>
@@ -229,7 +550,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +583,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF05073B"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -743,16 +1070,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -761,128 +1085,136 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1202,191 +1534,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L34"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="9.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
     <col min="6" max="7" width="12.25" style="1" customWidth="1"/>
-    <col min="8" max="10" width="11.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="8" max="11" width="11.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="11:12">
-      <c r="K1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customHeight="1" spans="3:13">
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="11:12">
-      <c r="K2" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:13">
       <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C5" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="1">
-        <v>100</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>500</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H7" s="2">
         <v>10000</v>
       </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>500</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C7" s="1">
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>200</v>
+      </c>
+      <c r="K7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="L7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>50</v>
-      </c>
-      <c r="K7" s="1" t="s">
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F8" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
         <v>10000</v>
@@ -1395,718 +1736,3387 @@
         <v>1</v>
       </c>
       <c r="J8" s="1">
-        <v>1000</v>
-      </c>
-      <c r="K8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="1">
+      <c r="E9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
-      <c r="C9" s="1">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>50</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
         <v>20</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="K10" s="2">
+        <v>2</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="1">
-        <v>20</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1000</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C10" s="1">
-        <v>5</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1" t="s">
+    </row>
+    <row r="11" customHeight="1" spans="3:13">
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="1">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1">
-        <v>50</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1">
+        <v>250</v>
+      </c>
+      <c r="H11" s="1">
+        <v>250</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="1">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1">
-        <v>50</v>
-      </c>
-      <c r="H11" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1">
-        <v>50</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:12">
-      <c r="C12" s="1">
+    </row>
+    <row r="12" customHeight="1" spans="3:13">
+      <c r="C12" s="2">
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="9" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="1">
+        <v>20</v>
+      </c>
+      <c r="G12" s="1">
+        <v>350</v>
+      </c>
+      <c r="H12" s="1">
+        <v>350</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C13" s="2">
+        <v>8</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1">
+        <v>450</v>
+      </c>
+      <c r="H13" s="1">
+        <v>450</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:13">
+      <c r="C14" s="2">
+        <v>9</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="1">
+        <v>7</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1250</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5250</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:13">
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="1">
+        <v>7</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1350</v>
+      </c>
+      <c r="H15" s="1">
+        <v>5350</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="1">
+        <v>7</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1450</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5450</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="2">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I17" s="2">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2">
+        <v>10</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C18" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="2">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>50</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
+      <c r="C19" s="2">
+        <v>14</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+      <c r="G19" s="2">
+        <v>500</v>
+      </c>
+      <c r="H19" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I19" s="1">
+        <v>30</v>
+      </c>
+      <c r="J19" s="1">
+        <v>3</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="20" customHeight="1" spans="1:12">
+      <c r="C20" s="2">
+        <v>15</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="1">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1500</v>
+      </c>
+      <c r="H20" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I20" s="1">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>50</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C21" s="2">
+        <v>16</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="2">
+        <v>5</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2500</v>
+      </c>
+      <c r="H21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C22" s="2">
+        <v>17</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="2">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2">
+        <v>3200</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C23" s="2">
+        <v>18</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1500</v>
+      </c>
+      <c r="H23" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I23" s="2">
+        <v>59</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C24" s="2">
+        <v>19</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1007</v>
+      </c>
+      <c r="H24" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I24" s="2">
+        <v>53</v>
+      </c>
+      <c r="J24" s="2">
+        <v>2</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C25" s="2">
+        <v>20</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>2003</v>
+      </c>
+      <c r="H25" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I25" s="2">
+        <v>61</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C26" s="2">
+        <v>21</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="2">
+        <v>3</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H26" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I26" s="2">
+        <v>5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>5</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C27" s="2">
+        <v>22</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="2">
+        <v>3</v>
+      </c>
+      <c r="G27" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H27" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I27" s="2">
+        <v>9</v>
+      </c>
+      <c r="J27" s="2">
+        <v>3</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>23</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2">
+        <v>6001</v>
+      </c>
+      <c r="H28" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I28" s="2">
+        <v>11</v>
+      </c>
+      <c r="J28" s="2">
+        <v>2</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C29" s="2">
+        <v>24</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2">
+        <v>4803</v>
+      </c>
+      <c r="H29" s="2">
+        <v>5800</v>
+      </c>
+      <c r="I29" s="2">
+        <v>7</v>
+      </c>
+      <c r="J29" s="2">
+        <v>5</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C30" s="2">
+        <v>25</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="2">
+        <v>20</v>
+      </c>
+      <c r="G30" s="2">
+        <v>4215</v>
+      </c>
+      <c r="H30" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I30" s="2">
+        <v>3</v>
+      </c>
+      <c r="J30" s="2">
+        <v>100</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C33" s="2">
+        <v>151</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="2">
+        <v>12</v>
+      </c>
+      <c r="G33" s="2">
+        <v>300</v>
+      </c>
+      <c r="H33" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2">
+        <v>25</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C34" s="2">
+        <v>152</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="2">
+        <v>6</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H34" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2">
+        <v>25</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C35" s="2">
+        <v>153</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="2">
+        <v>3</v>
+      </c>
+      <c r="G35" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H35" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>15</v>
+      </c>
+      <c r="K35" s="2">
+        <v>2</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C37" s="1">
+        <v>100</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="1">
+        <v>50</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1">
+        <v>300</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C38" s="1">
+        <v>101</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38" s="1">
+        <v>50</v>
+      </c>
+      <c r="G38" s="1">
+        <v>301</v>
+      </c>
+      <c r="H38" s="1">
+        <v>600</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K38" s="2">
+        <v>2</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
+        <v>102</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="1">
+        <v>50</v>
+      </c>
+      <c r="G39" s="1">
+        <v>601</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1</v>
+      </c>
+      <c r="J39" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K39" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="1">
+      <c r="L39" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:12">
+      <c r="C40" s="1">
+        <v>103</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F40" s="1">
+        <v>50</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K40" s="2">
+        <v>10</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C41" s="1">
+        <v>104</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="2">
+        <v>50</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H41" s="2">
+        <v>3500</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K41" s="2">
+        <v>20</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C42" s="1">
+        <v>105</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F42" s="2">
+        <v>50</v>
+      </c>
+      <c r="G42" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H42" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K42" s="2">
+        <v>40</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C44" s="2">
+        <v>200</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="2">
+        <v>50</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2">
+        <v>300</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C45" s="2">
+        <v>201</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" s="2">
+        <v>50</v>
+      </c>
+      <c r="G45" s="2">
+        <v>301</v>
+      </c>
+      <c r="H45" s="2">
+        <v>600</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1</v>
+      </c>
+      <c r="J45" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K45" s="2">
+        <v>2</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C46" s="2">
+        <v>202</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" s="2">
+        <v>50</v>
+      </c>
+      <c r="G46" s="2">
+        <v>601</v>
+      </c>
+      <c r="H46" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I46" s="2">
+        <v>1</v>
+      </c>
+      <c r="J46" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K46" s="2">
+        <v>4</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C47" s="2">
+        <v>203</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F47" s="2">
+        <v>50</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H47" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I47" s="2">
+        <v>1</v>
+      </c>
+      <c r="J47" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K47" s="2">
+        <v>10</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C48" s="2">
+        <v>204</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" s="2">
+        <v>50</v>
+      </c>
+      <c r="G48" s="2">
+        <v>1501</v>
+      </c>
+      <c r="H48" s="2">
+        <v>3500</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1</v>
+      </c>
+      <c r="J48" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K48" s="2">
+        <v>20</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C49" s="2">
+        <v>205</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" s="2">
+        <v>50</v>
+      </c>
+      <c r="G49" s="2">
+        <v>3501</v>
+      </c>
+      <c r="H49" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I49" s="2">
+        <v>1</v>
+      </c>
+      <c r="J49" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K49" s="2">
+        <v>40</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="D50" s="4"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C51" s="2">
+        <v>300</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F51" s="2">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K51" s="2">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C52" s="2">
+        <v>301</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F52" s="2">
+        <v>10</v>
+      </c>
+      <c r="G52" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H52" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K52" s="2">
+        <v>2</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C53" s="2">
+        <v>302</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F53" s="2">
+        <v>10</v>
+      </c>
+      <c r="G53" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H53" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+      <c r="J53" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K53" s="2">
+        <v>3</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1"/>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C55" s="2">
+        <v>400</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F55" s="2">
+        <v>10</v>
+      </c>
+      <c r="G55" s="2">
+        <v>50</v>
+      </c>
+      <c r="H55" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I55" s="2">
+        <v>1</v>
+      </c>
+      <c r="J55" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K55" s="2">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C56" s="2">
+        <v>401</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F56" s="2">
+        <v>10</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H56" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K56" s="2">
+        <v>2</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C57" s="2">
+        <v>402</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F57" s="2">
+        <v>10</v>
+      </c>
+      <c r="G57" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H57" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I57" s="2">
+        <v>1</v>
+      </c>
+      <c r="J57" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K57" s="2">
+        <v>3</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1"/>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C59" s="2">
+        <v>500</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F59" s="2">
+        <v>4</v>
+      </c>
+      <c r="G59" s="2">
         <v>150</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H59" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I59" s="2">
+        <v>1</v>
+      </c>
+      <c r="J59" s="2">
+        <v>20</v>
+      </c>
+      <c r="K59" s="2">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C60" s="2">
+        <v>501</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F60" s="2">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H60" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I60" s="2">
+        <v>1</v>
+      </c>
+      <c r="J60" s="2">
+        <v>20</v>
+      </c>
+      <c r="K60" s="2">
+        <v>2</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C61" s="2">
+        <v>502</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F61" s="2">
+        <v>4</v>
+      </c>
+      <c r="G61" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H61" s="2">
         <v>10000</v>
       </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="I61" s="2">
+        <v>1</v>
+      </c>
+      <c r="J61" s="2">
         <v>20</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="K61" s="2">
+        <v>3</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1"/>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C63" s="2">
+        <v>600</v>
+      </c>
+      <c r="D63" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F63" s="2">
+        <v>10</v>
+      </c>
+      <c r="G63" s="2">
+        <v>1</v>
+      </c>
+      <c r="H63" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K63" s="2">
+        <v>1</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C64" s="2">
+        <v>601</v>
+      </c>
+      <c r="D64" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F64" s="2">
+        <v>10</v>
+      </c>
+      <c r="G64" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H64" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I64" s="2">
+        <v>1</v>
+      </c>
+      <c r="J64" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K64" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:12">
-      <c r="C13" s="1">
+      <c r="L64" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C65" s="2">
+        <v>602</v>
+      </c>
+      <c r="D65" s="2">
+        <v>3001</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F65" s="2">
+        <v>10</v>
+      </c>
+      <c r="G65" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H65" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I65" s="2">
+        <v>1</v>
+      </c>
+      <c r="J65" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K65" s="2">
+        <v>3</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C67" s="2">
+        <v>700</v>
+      </c>
+      <c r="D67" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F67" s="2">
+        <v>10</v>
+      </c>
+      <c r="G67" s="2">
+        <v>200</v>
+      </c>
+      <c r="H67" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I67" s="2">
+        <v>1</v>
+      </c>
+      <c r="J67" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C68" s="2">
+        <v>701</v>
+      </c>
+      <c r="D68" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F68" s="2">
+        <v>10</v>
+      </c>
+      <c r="G68" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H68" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I68" s="2">
+        <v>1</v>
+      </c>
+      <c r="J68" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K68" s="2">
+        <v>2</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C69" s="2">
+        <v>702</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3002</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F69" s="2">
+        <v>10</v>
+      </c>
+      <c r="G69" s="2">
+        <v>3001</v>
+      </c>
+      <c r="H69" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I69" s="2">
+        <v>1</v>
+      </c>
+      <c r="J69" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K69" s="2">
+        <v>3</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:12">
+      <c r="K70" s="2"/>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C71" s="2">
+        <v>800</v>
+      </c>
+      <c r="D71" s="2">
+        <v>3003</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F71" s="2">
+        <v>2</v>
+      </c>
+      <c r="G71" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H71" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I71" s="2">
+        <v>7</v>
+      </c>
+      <c r="J71" s="2">
+        <v>13</v>
+      </c>
+      <c r="K71" s="2">
+        <v>5</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C72" s="2">
+        <v>801</v>
+      </c>
+      <c r="D72" s="2">
+        <v>3004</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F72" s="2">
+        <v>2</v>
+      </c>
+      <c r="G72" s="2">
+        <v>4001</v>
+      </c>
+      <c r="H72" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I72" s="2">
+        <v>13</v>
+      </c>
+      <c r="J72" s="2">
+        <v>5</v>
+      </c>
+      <c r="K72" s="2">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C73" s="2">
+        <v>802</v>
+      </c>
+      <c r="D73" s="2">
+        <v>3003</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73" s="2">
+        <v>3</v>
+      </c>
+      <c r="G73" s="2">
+        <v>5500</v>
+      </c>
+      <c r="H73" s="2">
+        <v>6500</v>
+      </c>
+      <c r="I73" s="2">
+        <v>7</v>
+      </c>
+      <c r="J73" s="2">
+        <v>20</v>
+      </c>
+      <c r="K73" s="2">
+        <v>7</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:12">
+      <c r="C75" s="1">
+        <v>901</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F75" s="1">
+        <v>20</v>
+      </c>
+      <c r="G75" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H75" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I75" s="1">
+        <v>3</v>
+      </c>
+      <c r="J75" s="1">
+        <v>30</v>
+      </c>
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:12">
+      <c r="C76" s="1">
+        <v>902</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" s="1">
+        <v>10</v>
+      </c>
+      <c r="G76" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H76" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I76" s="1">
+        <v>3</v>
+      </c>
+      <c r="J76" s="1">
+        <v>5</v>
+      </c>
+      <c r="K76" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:12">
+      <c r="C77" s="1">
+        <v>903</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F77" s="1">
+        <v>5</v>
+      </c>
+      <c r="G77" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H77" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I77" s="1">
+        <v>3</v>
+      </c>
+      <c r="J77" s="1">
+        <v>3</v>
+      </c>
+      <c r="K77" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:12">
+      <c r="C78" s="1">
+        <v>904</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F78" s="1">
+        <v>2</v>
+      </c>
+      <c r="G78" s="1">
+        <v>3501</v>
+      </c>
+      <c r="H78" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I78" s="1">
+        <v>4</v>
+      </c>
+      <c r="J78" s="1">
+        <v>6</v>
+      </c>
+      <c r="K78" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:12">
+      <c r="C79" s="1">
+        <v>905</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F79" s="1">
+        <v>10</v>
+      </c>
+      <c r="G79" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H79" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I79" s="1">
+        <v>3</v>
+      </c>
+      <c r="J79" s="1">
+        <v>20</v>
+      </c>
+      <c r="K79" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:12">
+      <c r="C80" s="1">
+        <v>906</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F80" s="1">
+        <v>5</v>
+      </c>
+      <c r="G80" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H80" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I80" s="1">
+        <v>3</v>
+      </c>
+      <c r="J80" s="1">
+        <v>3</v>
+      </c>
+      <c r="K80" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:12">
+      <c r="C81" s="1">
+        <v>907</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F81" s="1">
+        <v>3</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H81" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I81" s="1">
+        <v>3</v>
+      </c>
+      <c r="J81" s="1">
+        <v>2</v>
+      </c>
+      <c r="K81" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:12">
+      <c r="C84" s="1">
+        <v>10001</v>
+      </c>
+      <c r="D84" s="6">
+        <v>180001</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F84" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G84" s="1">
+        <v>100</v>
+      </c>
+      <c r="H84" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I84" s="1">
+        <v>100</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1</v>
+      </c>
+      <c r="K84" s="2">
+        <v>1</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:12">
+      <c r="C85" s="1">
+        <v>10002</v>
+      </c>
+      <c r="D85" s="6">
+        <v>180002</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F85" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G85" s="1">
+        <v>100</v>
+      </c>
+      <c r="H85" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I85" s="1">
+        <v>100</v>
+      </c>
+      <c r="J85" s="1">
+        <v>1</v>
+      </c>
+      <c r="K85" s="2">
+        <v>1</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:12">
+      <c r="C86" s="1">
+        <v>10003</v>
+      </c>
+      <c r="D86" s="6">
+        <v>180003</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F86" s="1">
+        <v>150000</v>
+      </c>
+      <c r="G86" s="1">
+        <v>100</v>
+      </c>
+      <c r="H86" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I86" s="1">
+        <v>100</v>
+      </c>
+      <c r="J86" s="1">
+        <v>5</v>
+      </c>
+      <c r="K86" s="2">
+        <v>1</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:12">
+      <c r="C87" s="1">
+        <v>10004</v>
+      </c>
+      <c r="D87" s="6">
+        <v>180004</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F87" s="1">
+        <v>8000</v>
+      </c>
+      <c r="G87" s="1">
+        <v>100</v>
+      </c>
+      <c r="H87" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I87" s="1">
+        <v>100</v>
+      </c>
+      <c r="J87" s="1">
+        <v>1</v>
+      </c>
+      <c r="K87" s="2">
+        <v>1</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:12">
+      <c r="C88" s="1">
+        <v>10005</v>
+      </c>
+      <c r="D88" s="6">
+        <v>180005</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F88" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G88" s="1">
+        <v>100</v>
+      </c>
+      <c r="H88" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I88" s="1">
+        <v>100</v>
+      </c>
+      <c r="J88" s="1">
+        <v>1</v>
+      </c>
+      <c r="K88" s="2">
+        <v>1</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:12">
+      <c r="C89" s="1">
+        <v>10006</v>
+      </c>
+      <c r="D89" s="6">
+        <v>180006</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F89" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G89" s="1">
+        <v>100</v>
+      </c>
+      <c r="H89" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I89" s="1">
+        <v>100</v>
+      </c>
+      <c r="J89" s="1">
+        <v>5</v>
+      </c>
+      <c r="K89" s="2">
+        <v>1</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:12">
+      <c r="C90" s="1">
+        <v>10007</v>
+      </c>
+      <c r="D90" s="6">
+        <v>180007</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F90" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G90" s="1">
+        <v>100</v>
+      </c>
+      <c r="H90" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I90" s="1">
+        <v>100</v>
+      </c>
+      <c r="J90" s="1">
+        <v>1</v>
+      </c>
+      <c r="K90" s="2">
+        <v>1</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:12">
+      <c r="C91" s="1">
+        <v>10008</v>
+      </c>
+      <c r="D91" s="6">
+        <v>180008</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F91" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G91" s="1">
+        <v>100</v>
+      </c>
+      <c r="H91" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I91" s="1">
+        <v>100</v>
+      </c>
+      <c r="J91" s="1">
+        <v>2</v>
+      </c>
+      <c r="K91" s="2">
+        <v>1</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:12">
+      <c r="C92" s="1">
+        <v>10009</v>
+      </c>
+      <c r="D92" s="6">
+        <v>180009</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F92" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G92" s="1">
+        <v>100</v>
+      </c>
+      <c r="H92" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I92" s="1">
+        <v>100</v>
+      </c>
+      <c r="J92" s="1">
+        <v>1</v>
+      </c>
+      <c r="K92" s="2">
+        <v>1</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:12">
+      <c r="C93" s="1">
+        <v>10010</v>
+      </c>
+      <c r="D93" s="6">
+        <v>180010</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F93" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G93" s="1">
+        <v>100</v>
+      </c>
+      <c r="H93" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I93" s="1">
+        <v>100</v>
+      </c>
+      <c r="J93" s="1">
+        <v>1</v>
+      </c>
+      <c r="K93" s="2">
+        <v>1</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:12">
+      <c r="C94" s="1">
+        <v>10011</v>
+      </c>
+      <c r="D94" s="6">
+        <v>180011</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F94" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G94" s="1">
+        <v>100</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I94" s="1">
+        <v>100</v>
+      </c>
+      <c r="J94" s="1">
+        <v>5</v>
+      </c>
+      <c r="K94" s="2">
+        <v>1</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:12">
+      <c r="C95" s="1">
+        <v>10012</v>
+      </c>
+      <c r="D95" s="6">
+        <v>180012</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F95" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G95" s="1">
+        <v>100</v>
+      </c>
+      <c r="H95" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I95" s="1">
+        <v>100</v>
+      </c>
+      <c r="J95" s="1">
+        <v>5</v>
+      </c>
+      <c r="K95" s="2">
+        <v>1</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:12">
+      <c r="C96" s="1">
+        <v>10013</v>
+      </c>
+      <c r="D96" s="6">
+        <v>180013</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G96" s="1">
+        <v>100</v>
+      </c>
+      <c r="H96" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I96" s="1">
+        <v>100</v>
+      </c>
+      <c r="J96" s="1">
+        <v>5</v>
+      </c>
+      <c r="K96" s="2">
+        <v>1</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:12">
+      <c r="C97" s="1">
+        <v>10014</v>
+      </c>
+      <c r="D97" s="6">
+        <v>180014</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F97" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G97" s="1">
+        <v>100</v>
+      </c>
+      <c r="H97" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I97" s="1">
+        <v>100</v>
+      </c>
+      <c r="J97" s="1">
+        <v>5</v>
+      </c>
+      <c r="K97" s="2">
+        <v>1</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:12">
+      <c r="C98" s="1">
+        <v>10015</v>
+      </c>
+      <c r="D98" s="6">
+        <v>180015</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F98" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G98" s="1">
+        <v>100</v>
+      </c>
+      <c r="H98" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I98" s="1">
+        <v>100</v>
+      </c>
+      <c r="J98" s="1">
+        <v>5</v>
+      </c>
+      <c r="K98" s="2">
+        <v>1</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:12">
+      <c r="C99" s="1">
+        <v>10016</v>
+      </c>
+      <c r="D99" s="6">
+        <v>180020</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F99" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G99" s="1">
+        <v>100</v>
+      </c>
+      <c r="H99" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I99" s="1">
+        <v>100</v>
+      </c>
+      <c r="J99" s="1">
+        <v>2</v>
+      </c>
+      <c r="K99" s="2">
+        <v>1</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:12">
+      <c r="C100" s="1">
+        <v>10017</v>
+      </c>
+      <c r="D100" s="6">
+        <v>180021</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F100" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G100" s="1">
+        <v>100</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I100" s="1">
+        <v>100</v>
+      </c>
+      <c r="J100" s="1">
+        <v>2</v>
+      </c>
+      <c r="K100" s="2">
+        <v>1</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:12">
+      <c r="C101" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D101" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F101" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G101" s="1">
+        <v>100</v>
+      </c>
+      <c r="H101" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I101" s="1">
+        <v>100</v>
+      </c>
+      <c r="J101" s="1">
+        <v>1</v>
+      </c>
+      <c r="K101" s="2">
+        <v>1</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:12">
+      <c r="C103" s="1">
+        <v>10030</v>
+      </c>
+      <c r="D103" s="1">
+        <v>180030</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F103" s="1">
+        <v>5</v>
+      </c>
+      <c r="G103" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H103" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I103" s="1">
+        <v>100</v>
+      </c>
+      <c r="J103" s="1">
+        <v>1</v>
+      </c>
+      <c r="K103" s="2">
+        <v>1</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="1:12">
+      <c r="C104" s="1">
+        <v>10031</v>
+      </c>
+      <c r="D104" s="6">
+        <v>180032</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F104" s="1">
+        <v>1</v>
+      </c>
+      <c r="G104" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H104" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I104" s="1">
+        <v>100</v>
+      </c>
+      <c r="J104" s="1">
+        <v>1</v>
+      </c>
+      <c r="K104" s="2">
+        <v>1</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:12">
+      <c r="C105" s="1">
+        <v>10032</v>
+      </c>
+      <c r="D105" s="6">
+        <v>180033</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F105" s="1">
+        <v>1</v>
+      </c>
+      <c r="G105" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H105" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I105" s="1">
+        <v>100</v>
+      </c>
+      <c r="J105" s="1">
+        <v>1</v>
+      </c>
+      <c r="K105" s="2">
+        <v>1</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:12">
+      <c r="C106" s="1">
+        <v>10033</v>
+      </c>
+      <c r="D106" s="6">
+        <v>180034</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F106" s="1">
+        <v>2</v>
+      </c>
+      <c r="G106" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H106" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I106" s="1">
+        <v>100</v>
+      </c>
+      <c r="J106" s="1">
+        <v>1</v>
+      </c>
+      <c r="K106" s="2">
+        <v>1</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="1:12">
+      <c r="C107" s="1">
+        <v>10034</v>
+      </c>
+      <c r="D107" s="6">
+        <v>180035</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F107" s="1">
+        <v>1</v>
+      </c>
+      <c r="G107" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H107" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I107" s="1">
+        <v>100</v>
+      </c>
+      <c r="J107" s="1">
+        <v>1</v>
+      </c>
+      <c r="K107" s="2">
+        <v>1</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="1:12">
+      <c r="C108" s="1">
+        <v>10035</v>
+      </c>
+      <c r="D108" s="6">
+        <v>180036</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F108" s="1">
+        <v>1</v>
+      </c>
+      <c r="G108" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H108" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I108" s="1">
+        <v>100</v>
+      </c>
+      <c r="J108" s="1">
+        <v>1</v>
+      </c>
+      <c r="K108" s="2">
+        <v>1</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="1:12">
+      <c r="C109" s="1">
+        <v>10036</v>
+      </c>
+      <c r="D109" s="6">
+        <v>180037</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F109" s="1">
+        <v>1</v>
+      </c>
+      <c r="G109" s="1">
+        <v>2500</v>
+      </c>
+      <c r="H109" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I109" s="1">
+        <v>100</v>
+      </c>
+      <c r="J109" s="1">
+        <v>1</v>
+      </c>
+      <c r="K109" s="2">
+        <v>1</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="1:12">
+      <c r="C110" s="1">
+        <v>10037</v>
+      </c>
+      <c r="D110" s="6">
+        <v>180038</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F110" s="1">
+        <v>4</v>
+      </c>
+      <c r="G110" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H110" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I110" s="1">
+        <v>100</v>
+      </c>
+      <c r="J110" s="1">
+        <v>1</v>
+      </c>
+      <c r="K110" s="2">
+        <v>1</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:12">
+      <c r="C111" s="1">
+        <v>10038</v>
+      </c>
+      <c r="D111" s="6">
+        <v>180039</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F111" s="1">
+        <v>3</v>
+      </c>
+      <c r="G111" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H111" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I111" s="1">
+        <v>100</v>
+      </c>
+      <c r="J111" s="1">
+        <v>1</v>
+      </c>
+      <c r="K111" s="2">
+        <v>1</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="1:12">
+      <c r="A112" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C112" s="1">
+        <v>10039</v>
+      </c>
+      <c r="D112" s="6">
+        <v>180040</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F112" s="1">
+        <v>2</v>
+      </c>
+      <c r="G112" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H112" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I112" s="1">
+        <v>100</v>
+      </c>
+      <c r="J112" s="1">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2">
+        <v>1</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:12">
+      <c r="C113" s="1">
+        <v>10040</v>
+      </c>
+      <c r="D113" s="6">
+        <v>180041</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F113" s="1">
+        <v>3</v>
+      </c>
+      <c r="G113" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H113" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I113" s="1">
+        <v>100</v>
+      </c>
+      <c r="J113" s="1">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:12">
+      <c r="C114" s="1">
+        <v>10041</v>
+      </c>
+      <c r="D114" s="6">
+        <v>180042</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F114" s="1">
+        <v>3</v>
+      </c>
+      <c r="G114" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H114" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I114" s="1">
+        <v>100</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:12">
+      <c r="C116" s="1">
+        <v>11001</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F116" s="1">
+        <v>5</v>
+      </c>
+      <c r="G116" s="1">
+        <v>150</v>
+      </c>
+      <c r="H116" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I116" s="1">
+        <v>20</v>
+      </c>
+      <c r="J116" s="1">
+        <v>2</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:12">
+      <c r="C117" s="1">
+        <v>11002</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F117" s="1">
+        <v>5</v>
+      </c>
+      <c r="G117" s="1">
+        <v>200</v>
+      </c>
+      <c r="H117" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I117" s="1">
+        <v>30</v>
+      </c>
+      <c r="J117" s="1">
+        <v>2</v>
+      </c>
+      <c r="K117" s="2">
+        <v>1</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:12">
+      <c r="C118" s="1">
+        <v>11003</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F118" s="1">
+        <v>15</v>
+      </c>
+      <c r="G118" s="1">
+        <v>1050</v>
+      </c>
+      <c r="H118" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I118" s="1">
+        <v>51</v>
+      </c>
+      <c r="J118" s="1">
+        <v>2</v>
+      </c>
+      <c r="K118" s="2">
+        <v>1</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:12">
+      <c r="C119" s="1">
+        <v>11004</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F119" s="1">
+        <v>5</v>
+      </c>
+      <c r="G119" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H119" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I119" s="1">
+        <v>79</v>
+      </c>
+      <c r="J119" s="1">
+        <v>2</v>
+      </c>
+      <c r="K119" s="2">
+        <v>1</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:12">
+      <c r="C120" s="1">
+        <v>11005</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F120" s="1">
+        <v>20</v>
+      </c>
+      <c r="G120" s="1">
+        <v>101</v>
+      </c>
+      <c r="H120" s="1">
+        <v>500</v>
+      </c>
+      <c r="I120" s="1">
+        <v>10</v>
+      </c>
+      <c r="J120" s="1">
+        <v>1</v>
+      </c>
+      <c r="K120" s="2">
+        <v>1</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:12">
+      <c r="C121" s="1">
+        <v>11006</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F121" s="1">
+        <v>15</v>
+      </c>
+      <c r="G121" s="1">
+        <v>501</v>
+      </c>
+      <c r="H121" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I121" s="1">
+        <v>10</v>
+      </c>
+      <c r="J121" s="1">
+        <v>1</v>
+      </c>
+      <c r="K121" s="2">
+        <v>1</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:12">
+      <c r="C122" s="1">
+        <v>11007</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F122" s="1">
+        <v>10</v>
+      </c>
+      <c r="G122" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H122" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I122" s="1">
+        <v>20</v>
+      </c>
+      <c r="J122" s="1">
+        <v>1</v>
+      </c>
+      <c r="K122" s="2">
+        <v>1</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:12">
+      <c r="C123" s="1">
+        <v>11008</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F123" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1">
+      <c r="G123" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H123" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I123" s="1">
+        <v>20</v>
+      </c>
+      <c r="J123" s="1">
+        <v>1</v>
+      </c>
+      <c r="K123" s="2">
+        <v>1</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:12">
+      <c r="C124" s="1">
+        <v>11009</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F124" s="1">
+        <v>15</v>
+      </c>
+      <c r="G124" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H124" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I124" s="1">
+        <v>52</v>
+      </c>
+      <c r="J124" s="1">
+        <v>1</v>
+      </c>
+      <c r="K124" s="2">
+        <v>1</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:12">
+      <c r="C125" s="1">
+        <v>11010</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F125" s="1">
+        <v>7</v>
+      </c>
+      <c r="G125" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H125" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I125" s="1">
+        <v>52</v>
+      </c>
+      <c r="J125" s="1">
+        <v>1</v>
+      </c>
+      <c r="K125" s="2">
+        <v>1</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:12">
+      <c r="C126" s="1">
+        <v>11011</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F126" s="1">
+        <v>3</v>
+      </c>
+      <c r="G126" s="1">
         <v>3001</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="1">
-        <v>10</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1">
-        <v>50</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:12">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1">
-        <v>3002</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="1">
-        <v>10</v>
-      </c>
-      <c r="G14" s="1">
-        <v>200</v>
-      </c>
-      <c r="H14" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="J14" s="1">
-        <v>50</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:12">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="1">
-        <v>30</v>
-      </c>
-      <c r="G15" s="1">
-        <v>250</v>
-      </c>
-      <c r="H15" s="1">
-        <v>250</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:12">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="1">
-        <v>10</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="J16" s="1">
-        <v>50</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="4:4">
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" customHeight="1" spans="4:4">
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" customHeight="1" spans="4:4">
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" customHeight="1" spans="3:11">
-      <c r="C20" s="1">
-        <v>101</v>
-      </c>
-      <c r="D20" s="4">
-        <v>180001</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I20" s="1">
-        <v>100</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:11">
-      <c r="C21" s="1">
-        <v>102</v>
-      </c>
-      <c r="D21" s="4">
-        <v>180002</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I21" s="1">
-        <v>100</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:11">
-      <c r="C22" s="1">
-        <v>103</v>
-      </c>
-      <c r="D22" s="4">
-        <v>180003</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I22" s="1">
-        <v>100</v>
-      </c>
-      <c r="J22" s="1">
-        <v>10</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:11">
-      <c r="C23" s="1">
-        <v>104</v>
-      </c>
-      <c r="D23" s="4">
-        <v>180004</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="1">
-        <v>8000</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I23" s="1">
-        <v>100</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:11">
-      <c r="C24" s="1">
-        <v>105</v>
-      </c>
-      <c r="D24" s="4">
-        <v>180005</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I24" s="1">
-        <v>100</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:11">
-      <c r="C25" s="1">
-        <v>106</v>
-      </c>
-      <c r="D25" s="4">
-        <v>180006</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I25" s="1">
-        <v>100</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:11">
-      <c r="C26" s="1">
-        <v>107</v>
-      </c>
-      <c r="D26" s="4">
-        <v>180007</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="H126" s="1">
+        <v>3800</v>
+      </c>
+      <c r="I126" s="1">
+        <v>62</v>
+      </c>
+      <c r="J126" s="1">
+        <v>1</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:12">
+      <c r="C127" s="1">
+        <v>11012</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F127" s="2">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H127" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I127" s="2">
+        <v>61</v>
+      </c>
+      <c r="J127" s="2">
+        <v>1</v>
+      </c>
+      <c r="K127" s="2">
+        <v>1</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:12">
+      <c r="C128" s="1">
+        <v>11013</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F128" s="1">
+        <v>3</v>
+      </c>
+      <c r="G128" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H128" s="1">
+        <v>6000</v>
+      </c>
+      <c r="I128" s="1">
         <v>43</v>
       </c>
-      <c r="F26" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G26" s="1">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I26" s="1">
-        <v>100</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:11">
-      <c r="C27" s="1">
-        <v>108</v>
-      </c>
-      <c r="D27" s="4">
-        <v>180008</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F27" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G27" s="1">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I27" s="1">
-        <v>100</v>
-      </c>
-      <c r="J27" s="1">
-        <v>2</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:11">
-      <c r="C28" s="1">
-        <v>109</v>
-      </c>
-      <c r="D28" s="4">
-        <v>180009</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G28" s="1">
-        <v>1</v>
-      </c>
-      <c r="H28" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I28" s="1">
-        <v>100</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:11">
-      <c r="C29" s="1">
-        <v>110</v>
-      </c>
-      <c r="D29" s="4">
-        <v>180010</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I29" s="1">
-        <v>100</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:11">
-      <c r="C30" s="1">
-        <v>111</v>
-      </c>
-      <c r="D30" s="4">
-        <v>180011</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F30" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I30" s="1">
-        <v>100</v>
-      </c>
-      <c r="J30" s="1">
-        <v>10</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:11">
-      <c r="C31" s="1">
-        <v>112</v>
-      </c>
-      <c r="D31" s="4">
-        <v>180012</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G31" s="1">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I31" s="1">
-        <v>100</v>
-      </c>
-      <c r="J31" s="1">
-        <v>10</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:11">
-      <c r="C32" s="1">
-        <v>113</v>
-      </c>
-      <c r="D32" s="4">
-        <v>180013</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F32" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G32" s="1">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I32" s="1">
-        <v>100</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:11">
-      <c r="C33" s="1">
-        <v>114</v>
-      </c>
-      <c r="D33" s="4">
-        <v>180014</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I33" s="1">
-        <v>100</v>
-      </c>
-      <c r="J33" s="1">
-        <v>10</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:11">
-      <c r="C34" s="1">
-        <v>115</v>
-      </c>
-      <c r="D34" s="4">
-        <v>180015</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F34" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G34" s="1">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I34" s="1">
-        <v>100</v>
-      </c>
-      <c r="J34" s="1">
-        <v>10</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>37</v>
+      <c r="J128" s="1">
+        <v>1</v>
+      </c>
+      <c r="K128" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:11">
+      <c r="C129" s="1">
+        <v>11014</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F129" s="1">
+        <v>3</v>
+      </c>
+      <c r="G129" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H129" s="1">
+        <v>6500</v>
+      </c>
+      <c r="I129" s="1">
+        <v>67</v>
+      </c>
+      <c r="J129" s="1">
+        <v>1</v>
+      </c>
+      <c r="K129" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3 E3 D4 D5 C4:C5 E4:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -787,7 +787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -805,9 +805,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1287,7 +1284,7 @@
         <v>100</v>
       </c>
       <c r="L6" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
@@ -1319,7 +1316,7 @@
         <v>100</v>
       </c>
       <c r="L7" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:14">
@@ -1329,7 +1326,7 @@
       <c r="D8" s="6">
         <v>3</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="3">
@@ -1365,7 +1362,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="3">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -1387,17 +1384,17 @@
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>8</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="3">
         <v>8</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -1415,21 +1412,21 @@
         <v>1000</v>
       </c>
       <c r="L10" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C11" s="7">
+      <c r="C11" s="3">
         <v>9</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="3">
         <v>9</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -1451,17 +1448,17 @@
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C12" s="7">
+      <c r="C12" s="3">
         <v>10</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="3">
         <v>10</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -1486,7 +1483,7 @@
       <c r="C13" s="2">
         <v>14</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="3">
         <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -1518,7 +1515,7 @@
       <c r="C14" s="2">
         <v>15</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="3">
         <v>15</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -1592,7 +1589,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2">
         <v>1000</v>
@@ -1698,7 +1695,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 D3:D5 E3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
